--- a/datos/PrTest 130826.xlsx
+++ b/datos/PrTest 130826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4811CE35-98C4-B64F-A16C-12A57001DC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA121F6A-80A6-EE48-B6AA-19FC0165AA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -1113,7 +1113,7 @@
         <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
